--- a/fix/issue-298-identity-status-rniv/ig/StructureDefinition-fr-core-location.xlsx
+++ b/fix/issue-298-identity-status-rniv/ig/StructureDefinition-fr-core-location.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-05T12:16:59+00:00</t>
+    <t>2026-06-05T12:18:27+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/fix/issue-298-identity-status-rniv/ig/StructureDefinition-fr-core-location.xlsx
+++ b/fix/issue-298-identity-status-rniv/ig/StructureDefinition-fr-core-location.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-05T12:18:27+00:00</t>
+    <t>2026-06-05T12:21:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/fix/issue-298-identity-status-rniv/ig/StructureDefinition-fr-core-location.xlsx
+++ b/fix/issue-298-identity-status-rniv/ig/StructureDefinition-fr-core-location.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-05T12:21:59+00:00</t>
+    <t>2026-06-05T13:35:06+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/fix/issue-298-identity-status-rniv/ig/StructureDefinition-fr-core-location.xlsx
+++ b/fix/issue-298-identity-status-rniv/ig/StructureDefinition-fr-core-location.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-05T13:35:06+00:00</t>
+    <t>2026-08-04T12:27:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -116,7 +116,7 @@
     <t>Base Definition</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/StructureDefinition/Location|4.0.1</t>
+    <t>http://hl7.eu/fhir/base/StructureDefinition/location-eu-core|2.0.0</t>
   </si>
   <si>
     <t>Abstract</t>
@@ -679,7 +679,7 @@
 </t>
   </si>
   <si>
-    <t>Unique code or number identifying the location to its users</t>
+    <t>Location identifier</t>
   </si>
   <si>
     <t>Unique code or number identifying the location to its users.</t>
@@ -730,13 +730,13 @@
     <t>The operational status if the location (where typically a bed/room).</t>
   </si>
   <si>
-    <t>http://terminology.hl7.org/ValueSet/v2-0116|2.9</t>
+    <t>http://terminology.hl7.org/ValueSet/v2-0116|3.0.0</t>
   </si>
   <si>
     <t>Location.name</t>
   </si>
   <si>
-    <t>Name of the location as used by humans</t>
+    <t>Location name</t>
   </si>
   <si>
     <t>Name of the location as used by humans. Does not need to be unique.</t>
@@ -767,7 +767,7 @@
     <t>Location.description</t>
   </si>
   <si>
-    <t>Additional details about the location that could be displayed as further information to identify the location beyond its name</t>
+    <t>Description of the location</t>
   </si>
   <si>
     <t>Description of the Location, which helps in finding or referencing the place.</t>
@@ -829,7 +829,7 @@
 </t>
   </si>
   <si>
-    <t>Contact details of the location</t>
+    <t>Location telecom</t>
   </si>
   <si>
     <t>The contact details of communication devices available at the location. This can include phone numbers, fax numbers, mobile numbers, email addresses and web sites.</t>
@@ -841,7 +841,7 @@
     <t>Location.address</t>
   </si>
   <si>
-    <t xml:space="preserve">Address
+    <t xml:space="preserve">Address {http://hl7.eu/fhir/base/StructureDefinition/Address-eu|2.0.0}
 </t>
   </si>
   <si>
@@ -863,7 +863,7 @@
     <t>Location.physicalType</t>
   </si>
   <si>
-    <t>Physical form of the location</t>
+    <t>Location type</t>
   </si>
   <si>
     <t>Physical form of the location, e.g. building, room, vehicle, road.</t>
@@ -964,13 +964,13 @@
 </t>
   </si>
   <si>
-    <t>Organization responsible for provisioning and upkeep</t>
+    <t>Managing organization</t>
   </si>
   <si>
     <t>The organization responsible for the provisioning and upkeep of the location.</t>
   </si>
   <si>
-    <t>This can also be used as the part of the organization hierarchy where this location provides services. These services can be defined through the HealthcareService resource.</t>
+    <t>The managing organization is the organization responsible for the location, such as a hospital or clinic.</t>
   </si>
   <si>
     <t>Need to know who manages the location.</t>
@@ -986,7 +986,7 @@
 </t>
   </si>
   <si>
-    <t>Another Location this one is physically a part of</t>
+    <t>Location this one is physically a part of</t>
   </si>
   <si>
     <t>Another Location of which this Location is physically a part of.</t>

--- a/fix/issue-298-identity-status-rniv/ig/StructureDefinition-fr-core-location.xlsx
+++ b/fix/issue-298-identity-status-rniv/ig/StructureDefinition-fr-core-location.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-04T12:27:17+00:00</t>
+    <t>2026-08-04T15:42:07+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/fix/issue-298-identity-status-rniv/ig/StructureDefinition-fr-core-location.xlsx
+++ b/fix/issue-298-identity-status-rniv/ig/StructureDefinition-fr-core-location.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-04T15:42:07+00:00</t>
+    <t>2026-08-07T07:47:42+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/fix/issue-298-identity-status-rniv/ig/StructureDefinition-fr-core-location.xlsx
+++ b/fix/issue-298-identity-status-rniv/ig/StructureDefinition-fr-core-location.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-07T07:47:42+00:00</t>
+    <t>2026-08-07T08:01:10+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/fix/issue-298-identity-status-rniv/ig/StructureDefinition-fr-core-location.xlsx
+++ b/fix/issue-298-identity-status-rniv/ig/StructureDefinition-fr-core-location.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-07T08:01:10+00:00</t>
+    <t>2026-08-07T08:58:25+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/fix/issue-298-identity-status-rniv/ig/StructureDefinition-fr-core-location.xlsx
+++ b/fix/issue-298-identity-status-rniv/ig/StructureDefinition-fr-core-location.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-07T08:58:25+00:00</t>
+    <t>2026-08-07T11:55:57+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/fix/issue-298-identity-status-rniv/ig/StructureDefinition-fr-core-location.xlsx
+++ b/fix/issue-298-identity-status-rniv/ig/StructureDefinition-fr-core-location.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-07T11:55:57+00:00</t>
+    <t>2026-08-10T12:42:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/fix/issue-298-identity-status-rniv/ig/StructureDefinition-fr-core-location.xlsx
+++ b/fix/issue-298-identity-status-rniv/ig/StructureDefinition-fr-core-location.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-10T12:42:53+00:00</t>
+    <t>2026-08-10T13:14:57+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/fix/issue-298-identity-status-rniv/ig/StructureDefinition-fr-core-location.xlsx
+++ b/fix/issue-298-identity-status-rniv/ig/StructureDefinition-fr-core-location.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-10T13:14:57+00:00</t>
+    <t>2026-08-10T13:29:34+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/fix/issue-298-identity-status-rniv/ig/StructureDefinition-fr-core-location.xlsx
+++ b/fix/issue-298-identity-status-rniv/ig/StructureDefinition-fr-core-location.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-10T13:29:34+00:00</t>
+    <t>2026-08-10T13:33:35+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/fix/issue-298-identity-status-rniv/ig/StructureDefinition-fr-core-location.xlsx
+++ b/fix/issue-298-identity-status-rniv/ig/StructureDefinition-fr-core-location.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-10T13:33:35+00:00</t>
+    <t>2026-08-10T13:39:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/fix/issue-298-identity-status-rniv/ig/StructureDefinition-fr-core-location.xlsx
+++ b/fix/issue-298-identity-status-rniv/ig/StructureDefinition-fr-core-location.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-10T13:39:12+00:00</t>
+    <t>2026-08-10T13:42:57+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/fix/issue-298-identity-status-rniv/ig/StructureDefinition-fr-core-location.xlsx
+++ b/fix/issue-298-identity-status-rniv/ig/StructureDefinition-fr-core-location.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-10T13:42:57+00:00</t>
+    <t>2026-08-10T13:45:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/fix/issue-298-identity-status-rniv/ig/StructureDefinition-fr-core-location.xlsx
+++ b/fix/issue-298-identity-status-rniv/ig/StructureDefinition-fr-core-location.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-10T13:45:29+00:00</t>
+    <t>2026-08-10T13:54:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/fix/issue-298-identity-status-rniv/ig/StructureDefinition-fr-core-location.xlsx
+++ b/fix/issue-298-identity-status-rniv/ig/StructureDefinition-fr-core-location.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-10T13:54:17+00:00</t>
+    <t>2026-08-10T14:12:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/fix/issue-298-identity-status-rniv/ig/StructureDefinition-fr-core-location.xlsx
+++ b/fix/issue-298-identity-status-rniv/ig/StructureDefinition-fr-core-location.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-10T14:12:55+00:00</t>
+    <t>2026-08-10T14:29:18+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/fix/issue-298-identity-status-rniv/ig/StructureDefinition-fr-core-location.xlsx
+++ b/fix/issue-298-identity-status-rniv/ig/StructureDefinition-fr-core-location.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-10T14:29:18+00:00</t>
+    <t>2026-08-10T16:19:09+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/fix/issue-298-identity-status-rniv/ig/StructureDefinition-fr-core-location.xlsx
+++ b/fix/issue-298-identity-status-rniv/ig/StructureDefinition-fr-core-location.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-10T16:19:09+00:00</t>
+    <t>2026-08-10T16:22:30+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/fix/issue-298-identity-status-rniv/ig/StructureDefinition-fr-core-location.xlsx
+++ b/fix/issue-298-identity-status-rniv/ig/StructureDefinition-fr-core-location.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-10T16:22:30+00:00</t>
+    <t>2026-08-10T16:46:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/fix/issue-298-identity-status-rniv/ig/StructureDefinition-fr-core-location.xlsx
+++ b/fix/issue-298-identity-status-rniv/ig/StructureDefinition-fr-core-location.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-10T16:46:59+00:00</t>
+    <t>2026-08-11T07:24:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/fix/issue-298-identity-status-rniv/ig/StructureDefinition-fr-core-location.xlsx
+++ b/fix/issue-298-identity-status-rniv/ig/StructureDefinition-fr-core-location.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-11T07:24:13+00:00</t>
+    <t>2026-08-11T10:04:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/fix/issue-298-identity-status-rniv/ig/StructureDefinition-fr-core-location.xlsx
+++ b/fix/issue-298-identity-status-rniv/ig/StructureDefinition-fr-core-location.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-11T10:04:20+00:00</t>
+    <t>2026-08-11T11:39:02+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/fix/issue-298-identity-status-rniv/ig/StructureDefinition-fr-core-location.xlsx
+++ b/fix/issue-298-identity-status-rniv/ig/StructureDefinition-fr-core-location.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-11T11:39:02+00:00</t>
+    <t>2026-08-12T13:53:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/fix/issue-298-identity-status-rniv/ig/StructureDefinition-fr-core-location.xlsx
+++ b/fix/issue-298-identity-status-rniv/ig/StructureDefinition-fr-core-location.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-12T13:53:29+00:00</t>
+    <t>2026-08-12T14:08:44+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
